--- a/AAII_Financials/Quarterly/BDX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BDX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
   <si>
     <t>BDX</t>
   </si>
@@ -656,544 +656,557 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4983000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4714000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4486000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5891000</v>
       </c>
-      <c r="G8" s="3">
-        <v>5509000</v>
-      </c>
       <c r="H8" s="3">
+        <v>4726000</v>
+      </c>
+      <c r="I8" s="3">
         <v>4480000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4333000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5437000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4990000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5045000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4706000</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="O8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4878000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4821000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4586000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4761000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4641000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4750000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4718000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4849000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4607000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9675000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5315000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4784000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3855000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4253000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4225000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4584000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4350000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4195000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4160000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4402000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4278000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4222000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3080000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3166000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3035000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2969000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2922000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>3231000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2668000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2560000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2434000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3092000</v>
       </c>
-      <c r="G9" s="3">
-        <v>2875000</v>
-      </c>
       <c r="H9" s="3">
+        <v>2491000</v>
+      </c>
+      <c r="I9" s="3">
         <v>2457000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2356000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2950000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2683000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2741000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2679000</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="O9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2688000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2586000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2453000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2684000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2574000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2637000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2498000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2762000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2649000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5089000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2583000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2519000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2195000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2480000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2247000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2318000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2276000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2221000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2187000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2309000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2262000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2619000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1527000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1612000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1532000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1537000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1470000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1679000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2315000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2154000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2052000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2799000</v>
       </c>
-      <c r="G10" s="3">
-        <v>2634000</v>
-      </c>
       <c r="H10" s="3">
+        <v>2235000</v>
+      </c>
+      <c r="I10" s="3">
         <v>2023000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1977000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2487000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2307000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2304000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2027000</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="O10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2190000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2235000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2133000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2077000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2067000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2113000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2220000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2087000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1958000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4586000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2732000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2265000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1660000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1773000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1978000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2266000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2074000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1974000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1973000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2093000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2016000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1603000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1553000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1554000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1503000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1432000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1452000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1552000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1236,130 +1249,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>258000</v>
+      </c>
+      <c r="E12" s="3">
         <v>249000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>235000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>322000</v>
       </c>
-      <c r="G12" s="3">
-        <v>297000</v>
-      </c>
       <c r="H12" s="3">
+        <v>230000</v>
+      </c>
+      <c r="I12" s="3">
         <v>232000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>244000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>302000</v>
-      </c>
-      <c r="K12" s="3">
-        <v>299000</v>
       </c>
       <c r="L12" s="3">
         <v>299000</v>
       </c>
       <c r="M12" s="3">
+        <v>299000</v>
+      </c>
+      <c r="N12" s="3">
         <v>290000</v>
       </c>
-      <c r="N12" s="3" t="s">
+      <c r="O12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>306000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>337000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>313000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>300000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>315000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>327000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>314000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>368000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>330000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>581000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>291000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>299000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>262000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>264000</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>270000</v>
       </c>
       <c r="AD12" s="3">
         <v>270000</v>
       </c>
       <c r="AE12" s="3">
+        <v>270000</v>
+      </c>
+      <c r="AF12" s="3">
         <v>282000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>252000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>258000</v>
-      </c>
-      <c r="AH12" s="3">
-        <v>277000</v>
       </c>
       <c r="AI12" s="3">
         <v>277000</v>
       </c>
       <c r="AJ12" s="3">
+        <v>277000</v>
+      </c>
+      <c r="AK12" s="3">
         <v>260000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>191000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>220000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>186000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>187000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>182000</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1480,175 +1497,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E14" s="3">
         <v>625000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>118000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>437000</v>
       </c>
-      <c r="G14" s="3">
-        <v>127000</v>
-      </c>
       <c r="H14" s="3">
+        <v>99000</v>
+      </c>
+      <c r="I14" s="3">
         <v>287000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>297000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>140000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>203000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>105000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>77000</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>160000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>65000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>50000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>84000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>68000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>29000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>17000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>265000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>48000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>169000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>61000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>133000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>74000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>115000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>86000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>199000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>90000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>101000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>91000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>140000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>145000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>117000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>354000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>111000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>112000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>76000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>129000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>407000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>563000</v>
+      </c>
+      <c r="E15" s="3">
         <v>520000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>614000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>629000</v>
       </c>
-      <c r="G15" s="3">
-        <v>618000</v>
-      </c>
       <c r="H15" s="3">
+        <v>575000</v>
+      </c>
+      <c r="I15" s="3">
         <v>524000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>607000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>586000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>568000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>571000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>561000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>587000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>571000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>563000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1724,8 +1747,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1765,252 +1791,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>4199000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4019000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3896000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4839000</v>
       </c>
-      <c r="G17" s="3">
-        <v>4528000</v>
-      </c>
       <c r="H17" s="3">
+        <v>3916000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3806000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3752000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4676000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4195000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4216000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4203000</v>
       </c>
-      <c r="N17" s="3" t="s">
+      <c r="O17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4169000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4140000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4001000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4294000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4106000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4186000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4026000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4617000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4115000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8297000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4085000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4529000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3497000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3883000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3724000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4473000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3724000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4059000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3272000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3826000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3766000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4052000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2845000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2723000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3289000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2523000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2153000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3135000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>784000</v>
+      </c>
+      <c r="E18" s="3">
         <v>695000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>590000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1052000</v>
       </c>
-      <c r="G18" s="3">
-        <v>981000</v>
-      </c>
       <c r="H18" s="3">
+        <v>810000</v>
+      </c>
+      <c r="I18" s="3">
         <v>674000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>581000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>761000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>795000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>829000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>503000</v>
       </c>
-      <c r="N18" s="3" t="s">
+      <c r="O18" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>709000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>681000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>585000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>467000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>535000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>564000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>692000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>232000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>492000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1378000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1230000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>255000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>358000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>370000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>501000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>111000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>626000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>136000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>888000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>576000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>512000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>170000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>235000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>443000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-254000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>446000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>769000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>96000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2053,618 +2086,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-109000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>12000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-45000</v>
       </c>
-      <c r="G20" s="3">
-        <v>4000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="I20" s="3">
         <v>41000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>14000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>7000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9000</v>
       </c>
-      <c r="N20" s="3" t="s">
+      <c r="O20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-17000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-43000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-15000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-25000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>6000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>30000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>28000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>45000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>11000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>25000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-36000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>29000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>28000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>38000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>19000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>317000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>21000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>28000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>40000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>34000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>2000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>18000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1377000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1324000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1192000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1726000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1595000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1391000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1157000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1174000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1340000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1360000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1408000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1073000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>587000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1297000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1264000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1150000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1005000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1074000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1087000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1244000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>844000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1028000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2519000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1830000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>819000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>917000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>871000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1060000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>692000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1190000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>737000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1448000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1161000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1397000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>744000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>554000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>769000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>59000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>709000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1049000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>377000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E22" s="3">
         <v>149000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>153000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>155000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>152000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>150000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>155000</v>
       </c>
       <c r="J22" s="3">
         <v>155000</v>
       </c>
       <c r="K22" s="3">
+        <v>155000</v>
+      </c>
+      <c r="L22" s="3">
         <v>137000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>125000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>111000</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="O22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>119000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>118000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>102000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>104000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>99000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>97000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>98000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>111000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>115000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>243000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>118000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>123000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>135000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>134000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>136000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>141000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>156000</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>171000</v>
       </c>
       <c r="AG22" s="3">
         <v>171000</v>
       </c>
       <c r="AH22" s="3">
+        <v>171000</v>
+      </c>
+      <c r="AI22" s="3">
         <v>181000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>182000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>185000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>158000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>157000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>184000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>86000</v>
-      </c>
-      <c r="AO22" s="3">
-        <v>95000</v>
       </c>
       <c r="AP22" s="3">
         <v>95000</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>95000</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>553000</v>
+      </c>
+      <c r="E23" s="3">
         <v>39000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>311000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>510000</v>
       </c>
-      <c r="G23" s="3">
-        <v>703000</v>
-      </c>
       <c r="H23" s="3">
+        <v>569000</v>
+      </c>
+      <c r="I23" s="3">
         <v>201000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>137000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>514000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>500000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>633000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>358000</v>
       </c>
-      <c r="N23" s="3" t="s">
+      <c r="O23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>471000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>528000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>481000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>320000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>421000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>442000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>600000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>151000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>378000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1163000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1157000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>143000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>248000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>200000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>394000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>460000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>714000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>414000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>647000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>6000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>105000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>326000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-404000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>362000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>692000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E24" s="3">
         <v>76000</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>17000</v>
       </c>
-      <c r="G24" s="3">
-        <v>129000</v>
-      </c>
       <c r="H24" s="3">
+        <v>118000</v>
+      </c>
+      <c r="I24" s="3">
         <v>43000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-10000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>114000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>13000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>96000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>77000</v>
       </c>
-      <c r="N24" s="3" t="s">
+      <c r="O24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>64000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>68000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-28000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>33000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>31000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>52000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>32000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-4000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-28000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>120000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>154000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>15000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-38000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>17000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>117000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-168000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>83000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>14000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>64000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>184000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>53000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>13000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-29000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-1000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-271000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>18000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>131000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2785,252 +2834,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>451000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-37000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>311000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>493000</v>
       </c>
-      <c r="G26" s="3">
-        <v>574000</v>
-      </c>
       <c r="H26" s="3">
+        <v>451000</v>
+      </c>
+      <c r="I26" s="3">
         <v>158000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>147000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>400000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>487000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>537000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>281000</v>
       </c>
-      <c r="N26" s="3" t="s">
+      <c r="O26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>407000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>460000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>509000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>287000</v>
-      </c>
-      <c r="S26" s="3">
-        <v>390000</v>
       </c>
       <c r="T26" s="3">
         <v>390000</v>
       </c>
       <c r="U26" s="3">
+        <v>390000</v>
+      </c>
+      <c r="V26" s="3">
         <v>568000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>155000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>406000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1043000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1003000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>128000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>286000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>183000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>277000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>166000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>377000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>650000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>230000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>594000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-7000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>134000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>327000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-133000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>344000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>561000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>377000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-311000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>383000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>493000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>574000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>308000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>303000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>400000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>487000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>537000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>281000</v>
       </c>
-      <c r="N27" s="3" t="s">
+      <c r="O27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>392000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>437000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>486000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>265000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>368000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>366000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>546000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>132000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>384000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>999000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>981000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>105000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>277000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>145000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>240000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>129000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>339000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-49000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>613000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>192000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>556000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-45000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>96000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>289000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-165000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>344000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>562000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3151,32 +3209,35 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-274000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>72000</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>123000</v>
+      </c>
+      <c r="I29" s="3">
         <v>150000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>156000</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
@@ -3202,25 +3263,25 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>-30000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>94000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>109000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>110000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>118000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>260000</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>24</v>
@@ -3234,32 +3295,32 @@
       <c r="AC29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>74000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>31000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-51000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-365000</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-5000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-270000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3273,8 +3334,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3395,8 +3459,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3517,252 +3584,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E32" s="3">
         <v>109000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-12000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>45000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-4000</v>
-      </c>
       <c r="H32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-41000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-14000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-7000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9000</v>
       </c>
-      <c r="N32" s="3" t="s">
+      <c r="O32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>17000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>20000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>43000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>15000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>25000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-6000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-30000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-45000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>36000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-28000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>10000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-38000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>3000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-19000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-317000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-28000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-40000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-18000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>377000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-311000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>383000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>493000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>574000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>308000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>303000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>400000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>487000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>537000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>281000</v>
       </c>
-      <c r="N33" s="3" t="s">
+      <c r="O33" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>407000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>460000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>486000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>265000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>338000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>460000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>655000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>242000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>502000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1259000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>981000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>105000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>277000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>145000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>240000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>125000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>413000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>562000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-173000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>556000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-50000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-174000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>289000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-165000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>344000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>562000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3883,257 +3959,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>377000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-311000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>383000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>493000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>574000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>308000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>303000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>400000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>487000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>537000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>281000</v>
       </c>
-      <c r="N35" s="3" t="s">
+      <c r="O35" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>407000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>460000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>486000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>265000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>338000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>460000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>655000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>242000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>502000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1259000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>981000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>105000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>277000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>145000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>240000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>125000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>413000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>562000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-173000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>556000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-50000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-174000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>289000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-165000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>344000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>562000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4176,8 +4261,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4220,740 +4306,759 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>708000</v>
+      </c>
+      <c r="E41" s="3">
         <v>813000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>740000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>641000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>735000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>667000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>711000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1717000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4459000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2348000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1180000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1416000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>923000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1981000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>612000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1006000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2558000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3147000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1903000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2283000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3153000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3734000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3248000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2825000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2882000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2351000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>560000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>536000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>523000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>686000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>943000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1140000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1384000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1251000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1124000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>14179000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>13852000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>548000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>919000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1541000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E42" s="3">
         <v>3000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>11000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>22000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>16000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>17000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>445000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>851000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>827000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2000</v>
-      </c>
-      <c r="N42" s="3">
-        <v>8000</v>
       </c>
       <c r="O42" s="3">
         <v>8000</v>
       </c>
       <c r="P42" s="3">
+        <v>8000</v>
+      </c>
+      <c r="Q42" s="3">
         <v>6000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
         <v>8000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>14000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>15000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>8000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>12000</v>
-      </c>
-      <c r="W42" s="3">
-        <v>24000</v>
       </c>
       <c r="X42" s="3">
         <v>24000</v>
       </c>
       <c r="Y42" s="3">
+        <v>24000</v>
+      </c>
+      <c r="Z42" s="3">
         <v>17000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>20000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>22000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>6000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>8000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>30000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>12000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>10000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>5000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>17000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>15000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>16000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>84000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>21000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>17000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>8000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>18000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2364000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2205000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2508000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2994000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2943000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3029000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2638000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3033000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2596000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2559000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2267000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2534000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2414000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2413000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2282000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2191000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2218000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2303000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2177000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2497000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2078000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2118000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2370000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2398000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1993000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2160000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2074000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2345000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2220000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2279000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2216000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2319000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2243000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2293000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2000000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1744000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1749000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1569000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1518000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1618000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3316000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3358000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4085000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3894000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3950000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3723000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3859000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3843000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3256000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3229000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3304000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3273000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3588000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3657000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3604000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3224000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3163000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3258000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3035000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2866000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2947000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2895000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2814000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2743000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2945000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2793000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2760000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2579000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2629000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2627000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2522000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2451000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2562000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2543000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2967000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1818000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1829000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1747000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1692000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1719000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F45" s="3">
         <v>1000</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H45" s="3">
-        <v>1000</v>
+      <c r="H45" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>24</v>
+      <c r="J45" s="3">
+        <v>1000</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M45" s="3">
         <v>1000</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P45" s="3">
         <v>272000</v>
       </c>
-      <c r="P45" s="3" t="s">
+      <c r="Q45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1677000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1712000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1594000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1429000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1184000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1180000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1336000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1229000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1088000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>983000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>985000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1245000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1036000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1174000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1397000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1242000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1255000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1484000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1321000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1409000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1367000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>871000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>765000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1019000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>1040000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>1462000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8139000</v>
+      </c>
+      <c r="E46" s="3">
         <v>8012000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9189000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9255000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8997000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8666000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8659000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10468000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12207000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10340000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8156000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8676000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8588000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9587000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8175000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8141000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9547000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10152000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8307000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>8838000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>9538000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10000000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9537000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8969000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8827000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8555000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6438000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6664000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6781000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6844000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6941000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7411000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7525000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7512000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>7542000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>18633000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>18212000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4891000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>5187000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>6367000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4996,8 +5101,8 @@
       <c r="P47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5074,252 +5179,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6083000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6082000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6972000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7882000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6818000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6646000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6602000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7697000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6518000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6591000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6646000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7074000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6473000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6356000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6247000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6012000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6005000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6406000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6384000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6393000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6164000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6142000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6096000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5923000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6260000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6091000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6208000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5659000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5550000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5473000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5362000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5375000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5321000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5411000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>5262000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>4638000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>4410000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3941000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>3827000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>3901000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>33965000</v>
+      </c>
+      <c r="E49" s="3">
         <v>34304000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>35645000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>36017000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>36385000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>36579000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>36818000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>37382000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>34456000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>34826000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>35211000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>35470000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>35897000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>36457000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>36753000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>36931000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>35855000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>36363000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>36727000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>36684000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>36811000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>37020000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>37315000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>37433000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>37658000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>37788000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>38160000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>38354000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>38839000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>39220000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>39567000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>40041000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>40147000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>40491000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>41375000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>13456000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>13562000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>13523000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>13560000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>13770000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5440,8 +5554,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5562,130 +5679,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2544000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2434000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3035000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>431000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2702000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2576000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2586000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>241000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2401000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2400000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2261000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>18000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2059000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1994000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1954000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1850000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1792000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1865000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1945000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1951000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1820000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1759000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1800000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1687000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1214000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1082000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1146000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1088000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1063000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1061000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1062000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1077000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>984000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1159000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1184000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1007000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>982000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1766000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1744000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1547000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5806,130 +5929,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>50731000</v>
+      </c>
+      <c r="E54" s="3">
         <v>50832000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>54841000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>55325000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>54902000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>54467000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>54665000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>57286000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>55582000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>54157000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>52274000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>52780000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>53017000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>54394000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>53129000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>52934000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>53199000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>54786000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>53363000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>53866000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>54333000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>54921000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>54748000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>54012000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>53959000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>53516000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>51952000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>51765000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>52233000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>52598000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>52932000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>53904000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>53977000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>54573000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>55363000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>37734000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>37166000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>24121000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>24318000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>25586000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5972,8 +6101,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6016,8 +6146,9 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -6027,23 +6158,23 @@
       <c r="E57" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G57" s="3">
         <v>1974000</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J57" s="3">
         <v>118000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1896000</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>24</v>
@@ -6051,279 +6182,285 @@
       <c r="M57" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O57" s="3">
         <v>1641000</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R57" s="3">
         <v>5437000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1699000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5398000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5605000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5671000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1793000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5716000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5375000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5284000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1355000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4333000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4295000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4164000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1092000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4069000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4050000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3891000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1106000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4207000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4224000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4185000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>797000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2819000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2785000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2581000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>3844000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3297000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2573000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2623000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1695000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1810000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1604000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1318000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2312000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1192000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>2016000</v>
       </c>
       <c r="M58" s="3">
         <v>2016000</v>
       </c>
       <c r="N58" s="3">
+        <v>2016000</v>
+      </c>
+      <c r="O58" s="3">
         <v>1258000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1856000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2214000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2188000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2179000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1682000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1051000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1064000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>500000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2033000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1737000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>707000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1630000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4357000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2456000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1309000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2168000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3057000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3254000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2601000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1900000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>202000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>703000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>203000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>453000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1224000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1974000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1001000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6107000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5934000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6138000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>811000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6350000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6087000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6228000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>650000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5413000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5311000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5524000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>552000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5022000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5090000</v>
       </c>
-      <c r="Q59" s="3" t="s">
+      <c r="R59" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3933000</v>
       </c>
-      <c r="S59" s="3" t="s">
+      <c r="T59" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1000</v>
       </c>
-      <c r="U59" s="3" t="s">
+      <c r="V59" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4333000</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>24</v>
@@ -6331,317 +6468,326 @@
       <c r="Y59" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="Z59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA59" s="3">
         <v>3774000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>104000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>103000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>106000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3254000</v>
       </c>
-      <c r="AE59" s="3" t="s">
+      <c r="AF59" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1000</v>
       </c>
-      <c r="AG59" s="3" t="s">
+      <c r="AH59" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3509000</v>
-      </c>
-      <c r="AI59" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AJ59" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL59" s="3">
         <v>7000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2342000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>9000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>15000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2734000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9404000</v>
+      </c>
+      <c r="E60" s="3">
         <v>8507000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8761000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8313000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8160000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7691000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7664000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8956000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6605000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7327000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7540000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6641000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6878000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7304000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7625000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7811000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7080000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6657000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6735000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6626000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7749000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5376000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7021000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5836000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6067000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8755000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6726000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5655000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6237000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7108000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7145000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7216000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6106000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4426000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4895000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3342000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3273000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>4018000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>4570000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>4400000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13511000</v>
+      </c>
+      <c r="E61" s="3">
         <v>14706000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16916000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18325000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17531000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17666000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>17440000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>18607000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>18131000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15995000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14094000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15152000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14926000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>16010000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14268000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13886000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14683000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>17584000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>16360000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>17110000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>15700000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>17718000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>16082000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>17224000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>17090000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>16809000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>16949000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>18081000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>18016000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>17556000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>17817000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>18894000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>20350000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>22589000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>22095000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>18667000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>18563000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>9082000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>9043000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>10550000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>24</v>
+      <c r="D62" s="3">
+        <v>1000</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G62" s="3">
         <v>457000</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>24</v>
@@ -6649,107 +6795,110 @@
       <c r="I62" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K62" s="3">
         <v>824000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1700000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1701000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1800000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1817000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1899000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1900000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5764000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5955000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5943000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6020000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6108000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6453000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6749000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7001000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>6982000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7187000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6780000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7001000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7075000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6948000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6483000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6625000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6566000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>6800000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>6164000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>6406000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>7126000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2777000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2743000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3058000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>3122000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>3003000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6870,8 +7019,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6992,8 +7144,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7114,130 +7269,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>26315000</v>
+      </c>
+      <c r="E66" s="3">
         <v>26699000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>29559000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>29935000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>29430000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>29226000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>29460000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>31396000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>29714000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28510000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26942000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26984000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>27080000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28705000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>27657000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>27652000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>27706000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>30261000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>29203000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>30189000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>30198000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>30095000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>30085000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>30247000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>29937000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>32565000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>30750000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>30684000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>30736000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>31289000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>31528000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>32910000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>32620000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>33421000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>34116000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>24786000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>24579000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>16158000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>16735000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>17953000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7280,8 +7441,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7402,8 +7564,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7524,8 +7689,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7566,7 +7734,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="3">
         <v>2000</v>
@@ -7632,7 +7800,7 @@
         <v>2000</v>
       </c>
       <c r="AL70" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AM70" s="3">
         <v>0</v>
@@ -7646,8 +7814,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7768,130 +7939,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17509000</v>
+      </c>
+      <c r="E72" s="3">
         <v>17391000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>16704000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16622000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16426000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16150000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>16141000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16139000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16015000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>15802000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15540000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15535000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15691000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15563000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15384000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15157000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15088000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14416000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14233000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>13826000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>13821000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>13557000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>13522000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12791000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>12916000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>12868000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12938000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>12913000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>12997000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12792000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13018000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>12596000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>12971000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>12616000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>12765000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>13111000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>12989000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>13321000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>13133000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>12727000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8012,8 +8189,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8134,8 +8314,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8256,130 +8439,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24416000</v>
+      </c>
+      <c r="E76" s="3">
         <v>24133000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>25282000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25390000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25472000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>25241000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>25205000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25890000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25868000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25647000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>25332000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>25796000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>25937000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>25687000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>25470000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>25280000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>25491000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>24523000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>24158000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>23675000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>24133000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>24824000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>24661000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>23763000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>24020000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20949000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>21200000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>21079000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>21495000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>21307000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>21402000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20992000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>21355000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>21150000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>21245000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>12948000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>12587000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>7963000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>7583000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>7633000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8500,257 +8689,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>377000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-311000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>383000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>493000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>574000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>308000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>303000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>400000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>487000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>537000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>281000</v>
       </c>
-      <c r="N81" s="3" t="s">
+      <c r="O81" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>407000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>460000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>486000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>265000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>338000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>460000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>655000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>242000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>502000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1259000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>981000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>105000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>277000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>145000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>240000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>125000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>413000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>562000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-173000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>556000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-50000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-174000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>289000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-165000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>344000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>562000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8793,130 +8991,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="3">
+        <v>187000</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>212000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>210000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>207000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>205000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>196000</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="K83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>204000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>197000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>202000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>215000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>197000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>196000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>567000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>581000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>534000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>557000</v>
       </c>
       <c r="U83" s="3">
         <v>557000</v>
       </c>
       <c r="V83" s="3">
+        <v>557000</v>
+      </c>
+      <c r="W83" s="3">
         <v>592000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>568000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1113000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>555000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>553000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>534000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>537000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>530000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>553000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>574000</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>563000</v>
       </c>
       <c r="AG83" s="3">
         <v>563000</v>
       </c>
       <c r="AH83" s="3">
+        <v>563000</v>
+      </c>
+      <c r="AI83" s="3">
         <v>566000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>568000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>553000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>291000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>286000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>279000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>261000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>262000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>273000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9037,8 +9239,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9159,8 +9364,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9281,8 +9489,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9403,8 +9614,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9525,130 +9739,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" s="3">
+        <v>725000</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>657000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1354000</v>
       </c>
-      <c r="G89" s="3">
-        <v>1219000</v>
-      </c>
-      <c r="H89" s="3" t="s">
+      <c r="H89" s="3">
+        <v>1211000</v>
+      </c>
+      <c r="I89" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>693000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1178000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1265000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>514000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>841000</v>
       </c>
-      <c r="N89" s="3" t="s">
+      <c r="O89" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1081000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>185000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>399000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>972000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>544000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>444000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>674000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>949000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>977000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2720000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1534000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1481000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>862000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>484000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>712000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1371000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>931000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>783000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>245000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1306000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>542000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>697000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>320000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1126000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>384000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>725000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>315000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>705000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9691,130 +9911,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="3">
+        <v>-143000</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-108000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-352000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-174000</v>
-      </c>
-      <c r="H91" s="3" t="s">
+      <c r="H91" s="3">
+        <v>-164000</v>
+      </c>
+      <c r="I91" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-105000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-296000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-179000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-134000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-116000</v>
       </c>
-      <c r="N91" s="3" t="s">
+      <c r="O91" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-191000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-181000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-208000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-315000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-253000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-222000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-183000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-452000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-243000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-499000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-246000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-213000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-202000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-222000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-173000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-358000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-237000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-195000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-167000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-307000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-197000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-213000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-178000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-260000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-195000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-160000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-112000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-294000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9935,8 +10159,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10057,130 +10284,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="3">
+        <v>-228000</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-183000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-494000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-336000</v>
-      </c>
-      <c r="H94" s="3" t="s">
+      <c r="H94" s="3">
+        <v>-337000</v>
+      </c>
+      <c r="I94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>204000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3937000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-288000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1056000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-233000</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-329000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-233000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-291000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2005000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-236000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-304000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-686000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-694000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-323000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-863000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-430000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-327000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-363000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-255000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-287000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-441000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-330000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-269000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>299000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-560000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>200000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-337000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-15203000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-347000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-381000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-203000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>48000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-351000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10223,31 +10456,32 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="3">
+        <v>286000</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>299000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>297000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>299000</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="I96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>302000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>275000</v>
       </c>
       <c r="K96" s="3">
         <v>275000</v>
@@ -10258,20 +10492,20 @@
       <c r="M96" s="3">
         <v>275000</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>24</v>
+      <c r="N96" s="3">
+        <v>275000</v>
       </c>
       <c r="O96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q96" s="3">
         <v>260000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-259000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-248000</v>
       </c>
       <c r="S96" s="3">
         <v>-248000</v>
@@ -10283,70 +10517,73 @@
         <v>-248000</v>
       </c>
       <c r="V96" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-235000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-239000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-484000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-242000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-367000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-230000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-215000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-214000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-209000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-208000</v>
       </c>
       <c r="AF96" s="3">
         <v>-208000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-208000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-207000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-928000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>374000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-239000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-210000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-199000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-166000</v>
-      </c>
-      <c r="AN96" s="3">
-        <v>-156000</v>
       </c>
       <c r="AO96" s="3">
         <v>-156000</v>
       </c>
       <c r="AP96" s="3">
+        <v>-156000</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-141000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10467,8 +10704,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10589,8 +10829,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10711,370 +10954,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="3">
+        <v>-651000</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-302000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-809000</v>
       </c>
-      <c r="G100" s="3">
-        <v>-841000</v>
-      </c>
-      <c r="H100" s="3" t="s">
+      <c r="H100" s="3">
+        <v>-838000</v>
+      </c>
+      <c r="I100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1928000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>124000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1120000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1705000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-862000</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1794000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1369000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-534000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-549000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-846000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1131000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-327000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1142000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1271000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-893000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-592000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1208000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>20000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1623000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-413000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-923000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-768000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-798000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-734000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1007000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-616000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-373000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1938000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-456000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>13294000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-906000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-955000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-485000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-12000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>7000</v>
       </c>
-      <c r="J101" s="3" t="s">
+      <c r="K101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>11000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-19000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-22000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>11000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-19000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-22000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-6000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>17000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>18000</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>6000</v>
       </c>
       <c r="AA101" s="3">
         <v>6000</v>
       </c>
       <c r="AB101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-21000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>6000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>10000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-34000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>27000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>2000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>5000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>6000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>13000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-30000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-152000</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>174000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>53000</v>
       </c>
-      <c r="G102" s="3">
-        <v>51000</v>
-      </c>
       <c r="H102" s="3">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1043000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2631000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2093000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1160000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-247000</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-1043000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1324000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-415000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1601000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-560000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1273000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-345000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-890000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-616000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>981000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>530000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-48000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>525000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1831000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>18000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-173000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-274000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-195000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-273000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>92000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>14000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-12943000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>328000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>13303000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-371000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-622000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-145000</v>
       </c>
     </row>
